--- a/Backtest/03-01-23/S&P500stock_03-01-23period252RS90.xlsx
+++ b/Backtest/03-01-23/S&P500stock_03-01-23period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
   <si>
     <t>Stock</t>
   </si>
@@ -127,67 +127,64 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t>TRGP</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>HES</t>
-  </si>
-  <si>
-    <t>APA</t>
+    <t>GEHC</t>
   </si>
   <si>
     <t>MPC</t>
   </si>
   <si>
-    <t>LW</t>
-  </si>
-  <si>
-    <t>SLB</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>HWM</t>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>GWW</t>
   </si>
   <si>
     <t>SMCI</t>
   </si>
   <si>
-    <t>2023-01-31</t>
-  </si>
-  <si>
-    <t>2023-02-22</t>
-  </si>
-  <si>
-    <t>2023-01-27</t>
-  </si>
-  <si>
-    <t>2023-01-25</t>
-  </si>
-  <si>
-    <t>2023-01-05</t>
-  </si>
-  <si>
-    <t>2023-01-20</t>
-  </si>
-  <si>
-    <t>2023-02-17</t>
-  </si>
-  <si>
-    <t>2023-02-14</t>
+    <t>WYNN</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>2023-04-25</t>
+  </si>
+  <si>
+    <t>2023-05-02</t>
+  </si>
+  <si>
+    <t>2023-05-25</t>
+  </si>
+  <si>
+    <t>2023-04-26</t>
+  </si>
+  <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
+    <t>2023-04-27</t>
+  </si>
+  <si>
+    <t>2023-05-09</t>
+  </si>
+  <si>
+    <t>2023-03-16</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Consumer Defensive</t>
+    <t>Consumer Cyclical</t>
   </si>
   <si>
     <t>Industrials</t>
@@ -196,31 +193,31 @@
     <t>Technology</t>
   </si>
   <si>
-    <t>Oil &amp; Gas Integrated</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
+    <t>Health Information Services</t>
   </si>
   <si>
     <t>Oil &amp; Gas Refining &amp; Marketing</t>
   </si>
   <si>
-    <t>Packaged Foods</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Farm &amp; Heavy Construction Machinery</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
   </si>
   <si>
     <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Resorts &amp; Casinos</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
   </si>
 </sst>
 </file>
@@ -578,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -699,58 +696,37 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>98.79275653923541</v>
+        <v>91.95171026156942</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="D2">
-        <v>110.3</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="F2">
-        <v>-0.6022865227125627</v>
-      </c>
-      <c r="G2">
-        <v>1.7</v>
-      </c>
-      <c r="H2">
-        <v>-0.6775868332605827</v>
+        <v>-0.07102109007506506</v>
       </c>
       <c r="I2">
-        <v>109.35</v>
+        <v>74.97800140380859</v>
       </c>
       <c r="J2">
-        <v>106.7344993591309</v>
+        <v>71.89200057983399</v>
       </c>
       <c r="K2">
-        <v>109.181799621582</v>
+        <v>65.90100021362305</v>
       </c>
       <c r="L2">
-        <v>95.45114971160889</v>
+        <v>62.66150840644435</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>7</v>
-      </c>
-      <c r="Q2">
-        <v>4</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>8.333333333333332</v>
+        <v>1.14</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -759,49 +735,49 @@
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>60.7</v>
+        <v>53</v>
       </c>
       <c r="Y2">
-        <v>114.66</v>
+        <v>76.98</v>
       </c>
       <c r="Z2">
-        <v>365.39</v>
+        <v>26.5</v>
       </c>
       <c r="AA2">
-        <v>9.65</v>
+        <v>0.83</v>
       </c>
       <c r="AB2">
-        <v>1675.36</v>
+        <v>390.7</v>
       </c>
       <c r="AC2">
-        <v>125</v>
+        <v>41.86</v>
       </c>
       <c r="AD2">
-        <v>10.46</v>
+        <v>6.07</v>
       </c>
       <c r="AE2">
-        <v>11.16</v>
+        <v>14.02</v>
       </c>
       <c r="AF2">
-        <v>228.91</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-38.46</v>
+        <v>24.42</v>
       </c>
       <c r="AH2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AJ2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AK2">
-        <v>90.27775388997001</v>
+        <v>70.96743106230174</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -809,40 +785,40 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.57344064386318</v>
+        <v>98.99396378269618</v>
       </c>
       <c r="C3">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="D3">
-        <v>73.5</v>
+        <v>123.6</v>
       </c>
       <c r="E3">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="F3">
-        <v>0.2633111933466977</v>
+        <v>0.08597289851192069</v>
       </c>
       <c r="G3">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="H3">
-        <v>0.2298955327134125</v>
+        <v>-0.1636066265372529</v>
       </c>
       <c r="I3">
-        <v>73.26799926757812</v>
+        <v>124.6799987792969</v>
       </c>
       <c r="J3">
-        <v>71.39449958801269</v>
+        <v>123.8180000305176</v>
       </c>
       <c r="K3">
-        <v>70.90139984130859</v>
+        <v>120.9882005310059</v>
       </c>
       <c r="L3">
-        <v>69.26654987335205</v>
+        <v>106.4247501754761</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
         <v>1.03</v>
@@ -863,55 +839,55 @@
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>51.26</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="Y3">
-        <v>81.5</v>
+        <v>136.46</v>
       </c>
       <c r="Z3">
-        <v>13.9</v>
+        <v>60.06</v>
       </c>
       <c r="AA3">
-        <v>-9.82</v>
+        <v>12.1</v>
       </c>
       <c r="AB3">
-        <v>1190</v>
+        <v>68.11</v>
       </c>
       <c r="AC3">
-        <v>158.22</v>
+        <v>344</v>
       </c>
       <c r="AD3">
-        <v>5.9</v>
+        <v>10.46</v>
       </c>
       <c r="AE3">
-        <v>-48.17</v>
+        <v>-26.97</v>
       </c>
       <c r="AF3">
-        <v>2633.33</v>
+        <v>-17.32</v>
       </c>
       <c r="AG3">
-        <v>104.11</v>
+        <v>635.33</v>
       </c>
       <c r="AH3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>79.29622731689456</v>
+        <v>66.92375136131665</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -919,59 +895,59 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>96.98189134808854</v>
+        <v>97.1830985915493</v>
       </c>
       <c r="C4">
-        <v>64</v>
+        <v>251</v>
       </c>
       <c r="D4">
-        <v>179.49</v>
+        <v>69.39</v>
       </c>
       <c r="E4">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="F4">
-        <v>-0.4802150499349748</v>
+        <v>-1.001771165269337</v>
       </c>
       <c r="G4">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="H4">
-        <v>-0.6412875386216228</v>
+        <v>-0.9942248843417679</v>
       </c>
       <c r="I4">
-        <v>178.3640014648437</v>
+        <v>67.65266723632813</v>
       </c>
       <c r="J4">
-        <v>174.0089996337891</v>
+        <v>68.97466659545898</v>
       </c>
       <c r="K4">
-        <v>178.3020001220703</v>
+        <v>67.8112661743164</v>
       </c>
       <c r="L4">
-        <v>164.072200012207</v>
+        <v>56.41956661224365</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>5</v>
       </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>9.444444444444443</v>
-      </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
@@ -982,46 +958,46 @@
         <v>1</v>
       </c>
       <c r="X4">
-        <v>117.13</v>
+        <v>35.49</v>
       </c>
       <c r="Y4">
-        <v>189.68</v>
+        <v>72.22</v>
       </c>
       <c r="Z4">
-        <v>278.72</v>
+        <v>10.61</v>
       </c>
       <c r="AA4">
-        <v>13.57</v>
+        <v>230.42</v>
       </c>
       <c r="AB4">
-        <v>125.7</v>
+        <v>5.27</v>
       </c>
       <c r="AC4">
-        <v>120.91</v>
+        <v>318.64</v>
       </c>
       <c r="AD4">
-        <v>7.04</v>
+        <v>15.75</v>
       </c>
       <c r="AE4">
-        <v>-2.84</v>
+        <v>175.47</v>
       </c>
       <c r="AF4">
-        <v>85.14</v>
+        <v>129.36</v>
       </c>
       <c r="AG4">
-        <v>22.81</v>
+        <v>-33.74</v>
       </c>
       <c r="AH4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI4" t="s">
         <v>56</v>
       </c>
       <c r="AJ4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AK4">
-        <v>65.29947360852829</v>
+        <v>43.30326291599795</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1029,43 +1005,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>99.59758551307847</v>
+        <v>97.78672032193158</v>
       </c>
       <c r="C5">
-        <v>303</v>
+        <v>431</v>
       </c>
       <c r="D5">
-        <v>141.82</v>
+        <v>468.53</v>
       </c>
       <c r="E5">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="F5">
-        <v>0.3742852595081415</v>
+        <v>-0.5644307684913055</v>
       </c>
       <c r="G5">
-        <v>2.52</v>
+        <v>2.13</v>
       </c>
       <c r="H5">
-        <v>0.3145938868709852</v>
+        <v>-0.2894578777197553</v>
       </c>
       <c r="I5">
-        <v>141.2820007324219</v>
+        <v>454.1839965820312</v>
       </c>
       <c r="J5">
-        <v>137.2280006408691</v>
+        <v>455.0139984130859</v>
       </c>
       <c r="K5">
-        <v>140.4031997680664</v>
+        <v>407.9119989013672</v>
       </c>
       <c r="L5">
-        <v>119.5677998352051</v>
+        <v>325.5436500549316</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1089,49 +1065,49 @@
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>73.41</v>
+        <v>230.54</v>
       </c>
       <c r="Y5">
-        <v>149.83</v>
+        <v>471.86</v>
       </c>
       <c r="Z5">
-        <v>33.67</v>
+        <v>25.23</v>
       </c>
       <c r="AA5">
-        <v>-0.14</v>
+        <v>1.82</v>
       </c>
       <c r="AB5">
-        <v>297.37</v>
+        <v>22.97</v>
       </c>
       <c r="AC5">
-        <v>91.95</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="AD5">
-        <v>7.4</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AE5">
-        <v>-22.33</v>
+        <v>4.72</v>
       </c>
       <c r="AF5">
-        <v>59.26</v>
+        <v>25.76</v>
       </c>
       <c r="AG5">
-        <v>55.17</v>
+        <v>36.29</v>
       </c>
       <c r="AH5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AJ5" t="s">
         <v>62</v>
       </c>
       <c r="AK5">
-        <v>62.43033504899266</v>
+        <v>39.55670270611665</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1139,43 +1115,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>98.18913480885311</v>
+        <v>90.3420523138833</v>
       </c>
       <c r="C6">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>46.68</v>
+        <v>77.41</v>
       </c>
       <c r="E6">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="F6">
-        <v>1.295370008648124</v>
+        <v>0.8260874161362811</v>
       </c>
       <c r="G6">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
       <c r="H6">
-        <v>1.040579779650181</v>
+        <v>0.604086005676011</v>
       </c>
       <c r="I6">
-        <v>46.53199996948242</v>
+        <v>77.6740005493164</v>
       </c>
       <c r="J6">
-        <v>45.02950000762939</v>
+        <v>81.19949951171876</v>
       </c>
       <c r="K6">
-        <v>45.82919990539551</v>
+        <v>71.61479988098145</v>
       </c>
       <c r="L6">
-        <v>40.94659994125366</v>
+        <v>65.72195003509522</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="N6">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1196,52 +1172,52 @@
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>26.53</v>
+        <v>44.76</v>
       </c>
       <c r="Y6">
-        <v>51.95</v>
+        <v>87.55</v>
       </c>
       <c r="Z6">
-        <v>11.28</v>
+        <v>27.95</v>
       </c>
       <c r="AA6">
-        <v>24.27</v>
+        <v>17.34</v>
       </c>
       <c r="AB6">
-        <v>298.86</v>
+        <v>22.28</v>
       </c>
       <c r="AC6">
-        <v>21.9</v>
+        <v>14.75</v>
       </c>
       <c r="AD6">
-        <v>34.17</v>
+        <v>9.74</v>
       </c>
       <c r="AE6">
-        <v>-52.94</v>
+        <v>94.44</v>
       </c>
       <c r="AF6">
-        <v>-50</v>
+        <v>-31.43</v>
       </c>
       <c r="AG6">
-        <v>418.1</v>
+        <v>-13.93</v>
       </c>
       <c r="AH6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AI6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AJ6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AK6">
-        <v>54.81744566578337</v>
+        <v>24.2815174540276</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1249,49 +1225,49 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.99396378269618</v>
+        <v>96.37826961770624</v>
       </c>
       <c r="C7">
-        <v>152</v>
+        <v>487</v>
       </c>
       <c r="D7">
-        <v>116.39</v>
+        <v>668.4299999999999</v>
       </c>
       <c r="E7">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="F7">
-        <v>0.008070841175377281</v>
+        <v>0.9830814047232669</v>
       </c>
       <c r="G7">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="H7">
-        <v>-0.2056960029541054</v>
+        <v>-0.1636066265372529</v>
       </c>
       <c r="I7">
-        <v>115.8059997558594</v>
+        <v>664.6380004882812</v>
       </c>
       <c r="J7">
-        <v>112.3925006866455</v>
+        <v>660.3720001220703</v>
       </c>
       <c r="K7">
-        <v>115.943800201416</v>
+        <v>601.8315979003906</v>
       </c>
       <c r="L7">
-        <v>99.31275012969971</v>
+        <v>546.172449645996</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -1300,58 +1276,58 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>63.29</v>
+        <v>440.48</v>
       </c>
       <c r="Y7">
-        <v>127.62</v>
+        <v>685.23</v>
       </c>
       <c r="Z7">
-        <v>49.07</v>
+        <v>28.42</v>
       </c>
       <c r="AA7">
-        <v>8.970000000000001</v>
+        <v>3.01</v>
       </c>
       <c r="AB7">
-        <v>46.55</v>
+        <v>11.72</v>
       </c>
       <c r="AC7">
-        <v>500</v>
+        <v>6.61</v>
       </c>
       <c r="AD7">
-        <v>15.3</v>
+        <v>14.52</v>
       </c>
       <c r="AE7">
-        <v>-17.32</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="AF7">
-        <v>635.33</v>
+        <v>15.1</v>
       </c>
       <c r="AG7">
-        <v>-1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AI7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AJ7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK7">
-        <v>54.3499311677075</v>
+        <v>9.603729546484697</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1359,43 +1335,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>94.96981891348088</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>277</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>89.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E8">
-        <v>0.88</v>
+        <v>3.78</v>
       </c>
       <c r="F8">
-        <v>-1.379104985842668</v>
+        <v>1.689554353364702</v>
       </c>
       <c r="G8">
-        <v>1.24</v>
+        <v>4.08</v>
       </c>
       <c r="H8">
-        <v>-1.234176017724633</v>
+        <v>2.16464152033904</v>
       </c>
       <c r="I8">
-        <v>89.37400054931641</v>
+        <v>9.564799880981445</v>
       </c>
       <c r="J8">
-        <v>87.60800094604492</v>
+        <v>8.881449985504151</v>
       </c>
       <c r="K8">
-        <v>85.73800033569336</v>
+        <v>8.327679958343506</v>
       </c>
       <c r="L8">
-        <v>75.42020004272462</v>
+        <v>6.678114988803864</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1413,55 +1389,55 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>49.71</v>
+        <v>3.41</v>
       </c>
       <c r="Y8">
-        <v>90.59999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="Z8">
-        <v>11.5</v>
+        <v>4.61</v>
       </c>
       <c r="AA8">
-        <v>7.33</v>
+        <v>2299.04</v>
       </c>
       <c r="AB8">
-        <v>40.2</v>
+        <v>179.49</v>
       </c>
       <c r="AC8">
-        <v>600</v>
+        <v>122.15</v>
       </c>
       <c r="AD8">
-        <v>45.47</v>
+        <v>9.69</v>
       </c>
       <c r="AE8">
-        <v>631.8200000000001</v>
+        <v>-5.7</v>
       </c>
       <c r="AF8">
-        <v>-69.86</v>
+        <v>28.57</v>
       </c>
       <c r="AG8">
-        <v>217.39</v>
+        <v>83.22</v>
       </c>
       <c r="AH8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AJ8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AK8">
-        <v>52.72724342876087</v>
+        <v>70.29260068538116</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1469,109 +1445,109 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>98.59154929577466</v>
+        <v>90.74446680080483</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="D9">
-        <v>53.46</v>
+        <v>108.37</v>
       </c>
       <c r="E9">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="F9">
-        <v>0.6961100513763282</v>
+        <v>-0.6092861938018729</v>
       </c>
       <c r="G9">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="H9">
-        <v>0.5807887142233572</v>
+        <v>-0.3020430028380052</v>
       </c>
       <c r="I9">
-        <v>53.09199981689453</v>
+        <v>106.5099990844727</v>
       </c>
       <c r="J9">
-        <v>51.17800006866455</v>
+        <v>106.2604999542236</v>
       </c>
       <c r="K9">
-        <v>51.78199989318848</v>
+        <v>97.58219970703125</v>
       </c>
       <c r="L9">
-        <v>42.50940001487732</v>
+        <v>73.26829980850219</v>
       </c>
       <c r="M9">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9">
-        <v>4.444444444444444</v>
+        <v>5.555555555555556</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>29.49</v>
+        <v>50.2</v>
       </c>
       <c r="Y9">
-        <v>56.04</v>
+        <v>111.77</v>
       </c>
       <c r="Z9">
-        <v>51.66</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AA9">
-        <v>-25.36</v>
+        <v>-2.63</v>
       </c>
       <c r="AB9">
-        <v>30.25</v>
+        <v>54.68</v>
       </c>
       <c r="AC9">
-        <v>48.84</v>
+        <v>116.98</v>
       </c>
       <c r="AD9">
-        <v>5.25</v>
+        <v>2.04</v>
       </c>
       <c r="AE9">
-        <v>-5.88</v>
+        <v>121.26</v>
       </c>
       <c r="AF9">
-        <v>88.89</v>
+        <v>-11.4</v>
       </c>
       <c r="AG9">
-        <v>-16.28</v>
+        <v>28.3</v>
       </c>
       <c r="AH9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AI9" t="s">
         <v>56</v>
       </c>
       <c r="AJ9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AK9">
-        <v>41.03406625291199</v>
+        <v>64.25735585811042</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1579,46 +1555,46 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>91.14688128772636</v>
+        <v>96.17706237424547</v>
       </c>
       <c r="C10">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="D10">
-        <v>428.76</v>
+        <v>83.03</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="F10">
-        <v>-1.245936106448936</v>
+        <v>-1.338186855098592</v>
       </c>
       <c r="G10">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="H10">
-        <v>-1.040579779650181</v>
+        <v>-0.8557885080410156</v>
       </c>
       <c r="I10">
-        <v>432.1320007324219</v>
+        <v>83.08200073242188</v>
       </c>
       <c r="J10">
-        <v>435.944499206543</v>
+        <v>82.70149955749511</v>
       </c>
       <c r="K10">
-        <v>418.4135992431641</v>
+        <v>76.74519989013672</v>
       </c>
       <c r="L10">
-        <v>375.0092994689941</v>
+        <v>64.63889995574951</v>
       </c>
       <c r="M10">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1630,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U10" t="b">
         <v>1</v>
@@ -1639,269 +1615,49 @@
         <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>283.81</v>
+        <v>48.8</v>
       </c>
       <c r="Y10">
-        <v>448.4</v>
+        <v>84.92</v>
       </c>
       <c r="Z10">
-        <v>121.24</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AA10">
-        <v>18.01</v>
+        <v>219.69</v>
       </c>
       <c r="AB10">
-        <v>6.07</v>
+        <v>6.68</v>
       </c>
       <c r="AC10">
-        <v>152.72</v>
+        <v>6.45</v>
       </c>
       <c r="AD10">
-        <v>11.07</v>
+        <v>8.81</v>
       </c>
       <c r="AE10">
-        <v>19.84</v>
+        <v>-27.63</v>
       </c>
       <c r="AF10">
-        <v>-9.49</v>
+        <v>47.1</v>
       </c>
       <c r="AG10">
-        <v>132.99</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AI10" t="s">
         <v>58</v>
       </c>
       <c r="AJ10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AK10">
-        <v>28.71839949644236</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11">
-        <v>90.54325955734407</v>
-      </c>
-      <c r="C11">
-        <v>171</v>
-      </c>
-      <c r="D11">
-        <v>39.41</v>
-      </c>
-      <c r="E11">
-        <v>1.5</v>
-      </c>
-      <c r="F11">
-        <v>-0.6910657756417177</v>
-      </c>
-      <c r="G11">
-        <v>1.83</v>
-      </c>
-      <c r="H11">
-        <v>-0.5202898898250901</v>
-      </c>
-      <c r="I11">
-        <v>39.19600067138672</v>
-      </c>
-      <c r="J11">
-        <v>38.57900028228759</v>
-      </c>
-      <c r="K11">
-        <v>37.35160011291504</v>
-      </c>
-      <c r="L11">
-        <v>35.32960001945496</v>
-      </c>
-      <c r="M11">
-        <v>1.02</v>
-      </c>
-      <c r="N11">
-        <v>1.05</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="b">
-        <v>1</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-      <c r="X11">
-        <v>29.35</v>
-      </c>
-      <c r="Y11">
-        <v>39.78</v>
-      </c>
-      <c r="Z11">
-        <v>12.99</v>
-      </c>
-      <c r="AA11">
-        <v>-2.08</v>
-      </c>
-      <c r="AB11">
-        <v>23.81</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>2.49</v>
-      </c>
-      <c r="AE11">
-        <v>-45.71</v>
-      </c>
-      <c r="AF11">
-        <v>12.9</v>
-      </c>
-      <c r="AG11">
-        <v>63.16</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK11">
-        <v>12.62613153874685</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12">
-        <v>99.19517102615694</v>
-      </c>
-      <c r="C12">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E12">
-        <v>3.71</v>
-      </c>
-      <c r="F12">
-        <v>1.761461086526187</v>
-      </c>
-      <c r="G12">
-        <v>4.04</v>
-      </c>
-      <c r="H12">
-        <v>2.153758148578282</v>
-      </c>
-      <c r="I12">
-        <v>8.19379997253418</v>
-      </c>
-      <c r="J12">
-        <v>8.398500037193298</v>
-      </c>
-      <c r="K12">
-        <v>8.11503999710083</v>
-      </c>
-      <c r="L12">
-        <v>5.864529989957809</v>
-      </c>
-      <c r="M12">
-        <v>0.98</v>
-      </c>
-      <c r="N12">
-        <v>1.01</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" t="b">
-        <v>0</v>
-      </c>
-      <c r="V12" t="b">
-        <v>1</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-      <c r="X12">
-        <v>3.41</v>
-      </c>
-      <c r="Y12">
-        <v>9.52</v>
-      </c>
-      <c r="Z12">
-        <v>3.03</v>
-      </c>
-      <c r="AA12">
-        <v>1270.81</v>
-      </c>
-      <c r="AB12">
-        <v>185</v>
-      </c>
-      <c r="AC12">
-        <v>328.05</v>
-      </c>
-      <c r="AD12">
-        <v>11.35</v>
-      </c>
-      <c r="AE12">
-        <v>28.57</v>
-      </c>
-      <c r="AF12">
-        <v>83.22</v>
-      </c>
-      <c r="AG12">
-        <v>81.70999999999999</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK12">
-        <v>64.59208070675686</v>
+        <v>2.698217991988686</v>
       </c>
     </row>
   </sheetData>
